--- a/AMLX.xlsx
+++ b/AMLX.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86F4F43-4722-4DF9-8CF6-3B33113EA85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA36361E-9E72-47F8-9114-666D058F1A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="540" windowWidth="34725" windowHeight="20565" xr2:uid="{614FE801-9ABF-4EC1-9E63-49FFB8BF4105}"/>
+    <workbookView xWindow="22320" yWindow="9010" windowWidth="14660" windowHeight="11930" activeTab="1" xr2:uid="{614FE801-9ABF-4EC1-9E63-49FFB8BF4105}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Model" sheetId="2" r:id="rId2"/>
-    <sheet name="Relyvrio" sheetId="3" r:id="rId3"/>
+    <sheet name="avexitide" sheetId="4" r:id="rId2"/>
+    <sheet name="Model" sheetId="2" r:id="rId3"/>
+    <sheet name="Relyvrio" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>Price</t>
   </si>
@@ -185,6 +186,30 @@
   </si>
   <si>
     <t>Phase II "CENTAUR"</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>avexitide</t>
+  </si>
+  <si>
+    <t>PBH</t>
+  </si>
+  <si>
+    <t>GLP-1 antagonist</t>
+  </si>
+  <si>
+    <t>Post-Bariatric Hypoglycemia</t>
+  </si>
+  <si>
+    <t>Phase III "LUCIDITY" 16-week RCT</t>
+  </si>
+  <si>
+    <t>placebo-controlled</t>
+  </si>
+  <si>
+    <t>Phase IIb "PREVENT"</t>
   </si>
 </sst>
 </file>
@@ -321,7 +346,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -336,7 +361,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -421,9 +445,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -461,7 +485,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -567,7 +591,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -709,7 +733,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -717,167 +741,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC4F142-3737-4346-ABC5-783D0BD9D72B}">
-  <dimension ref="B2:P9"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:M9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.81640625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="14"/>
+      <c r="F2" s="13"/>
       <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="15"/>
-      <c r="N2" t="s">
+      <c r="K2" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="1">
-        <v>26.7</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="L2" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
       <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="9"/>
-      <c r="N3" t="s">
+      <c r="K3" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="2">
-        <v>67.176067000000003</v>
-      </c>
-      <c r="P3" s="3" t="s">
+      <c r="L3" s="2">
+        <v>111.42304799999999</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="K4" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2">
+        <f>L2*L3</f>
+        <v>2674.1531519999999</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="K5" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
+        <f>49.326+201.434</f>
+        <v>250.76</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="K6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="2">
-        <f>O2*O3</f>
-        <v>1793.6009888999999</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
-      <c r="N5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="2">
-        <f>114.563+231.111</f>
-        <v>345.67399999999998</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9"/>
-      <c r="N6" t="s">
-        <v>4</v>
-      </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
-      <c r="N7" t="s">
+      <c r="K7" t="s">
         <v>5</v>
       </c>
-      <c r="O7" s="2">
-        <f>O4-O5+O6</f>
-        <v>1447.9269889</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="L7" s="2">
+        <f>L4-L5+L6</f>
+        <v>2423.3931519999996</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="12"/>
-      <c r="N9" t="s">
+      <c r="K9" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="2">
+      <c r="L9" s="2">
         <v>352.64699999999999</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -887,21 +872,81 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60C8ABA3-8CD3-4698-960D-2703C800CC31}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B34FE3-88F0-4FBD-8E17-27D6B77E473F}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="9.140625" style="3"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
@@ -951,7 +996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
@@ -976,7 +1021,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
@@ -1001,7 +1046,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
     </row>
-    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
@@ -1028,7 +1073,7 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1053,7 +1098,7 @@
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
@@ -1078,7 +1123,7 @@
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
     </row>
-    <row r="8" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
@@ -1105,7 +1150,7 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
@@ -1132,7 +1177,7 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
     </row>
-    <row r="10" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
@@ -1159,7 +1204,7 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
     </row>
-    <row r="11" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>35</v>
       </c>
@@ -1186,7 +1231,7 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
-    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -1211,7 +1256,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
     </row>
-    <row r="13" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
@@ -1238,7 +1283,7 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -1251,7 +1296,7 @@
         <v>2.2197553569942911E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>1</v>
       </c>
@@ -1271,21 +1316,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7DC2FC-1017-4346-9C4B-40BE4DF860ED}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>42</v>
       </c>
@@ -1293,7 +1338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>44</v>
       </c>
@@ -1301,7 +1346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>38</v>
       </c>
@@ -1309,18 +1354,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C6" s="16" t="s">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C10" s="16" t="s">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="15" t="s">
         <v>48</v>
       </c>
     </row>
